--- a/stage4_course_extraction/output/07_课程教学要素证据索引.xlsx
+++ b/stage4_course_extraction/output/07_课程教学要素证据索引.xlsx
@@ -17,10 +17,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'课程文档'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'原文证据'!$A$1:$L$160</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'实体证据多对多关联'!$A$1:$G$241</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'教学要素实体'!$A$1:$E$227</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'教学要素关系'!$A$1:$E$243</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'数据字典'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'实体证据多对多关联'!$A$1:$G$245</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'教学要素实体'!$A$1:$E$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'教学要素关系'!$A$1:$E$245</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'数据字典'!$A$1:$B$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -9935,7 +9935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G241"/>
+  <dimension ref="A1:G245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15388,7 +15388,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CK015</t>
+          <t>CK060</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -18224,8 +18224,148 @@
         </is>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>CTB001</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>CE12-25ece1edeb</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>P08学生实践要求</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>原文明示</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>待审查</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>EL0241</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>CTB001</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>CE12-7b942d42b5</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>P08教师检查反馈</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>原文明示</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>一般答疑纠错，不是单独备份或恢复评分规则</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>待审查</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>EL0242</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>CTB002</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>CE12-25ece1edeb</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>P08学生实践要求</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>原文明示</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>待审查</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>EL0243</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>CTB002</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>CE12-7b942d42b5</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>P08教师检查反馈</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>原文明示</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>一般答疑纠错，不是单独备份或恢复评分规则</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>待审查</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>EL0244</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G241"/>
+  <autoFilter ref="A1:G245"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18236,7 +18376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E227"/>
+  <dimension ref="A1:E230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -22191,17 +22331,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>KO056</t>
+          <t>CK060</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>知识点项目出现记录</t>
+          <t>规范化知识技能点</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>P07 CREATE TABLE创建数据表</t>
+          <t>建表时定义索引</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -22218,17 +22358,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CK055</t>
+          <t>KO056</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>规范化知识技能点</t>
+          <t>知识点项目出现记录</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>索引删除与维护</t>
+          <t>P07 建表时定义索引</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -22245,17 +22385,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>KO057</t>
+          <t>CK055</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>知识点项目出现记录</t>
+          <t>规范化知识技能点</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>P07 索引删除与维护</t>
+          <t>索引删除与维护</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -22272,17 +22412,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CK056</t>
+          <t>KO057</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>规范化知识技能点</t>
+          <t>知识点项目出现记录</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>索引查询效果对比</t>
+          <t>P07 索引删除与维护</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -22299,17 +22439,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>KO058</t>
+          <t>CK056</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>知识点项目出现记录</t>
+          <t>规范化知识技能点</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>P07 索引查询效果对比</t>
+          <t>索引查询效果对比</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -22326,17 +22466,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CK057</t>
+          <t>KO058</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>规范化知识技能点</t>
+          <t>知识点项目出现记录</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>数据库备份与恢复</t>
+          <t>P07 索引查询效果对比</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -22353,17 +22493,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>KO059</t>
+          <t>CK057</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>知识点项目出现记录</t>
+          <t>规范化知识技能点</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>P08 数据库备份与恢复</t>
+          <t>数据库备份与恢复</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -22380,17 +22520,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CK058</t>
+          <t>KO059</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>规范化知识技能点</t>
+          <t>知识点项目出现记录</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>事务概念与ACID</t>
+          <t>P08 数据库备份与恢复</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -22407,17 +22547,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>KO060</t>
+          <t>CK058</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>知识点项目出现记录</t>
+          <t>规范化知识技能点</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>P08 事务概念与ACID</t>
+          <t>事务概念与ACID</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -22434,17 +22574,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CK059</t>
+          <t>KO060</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>规范化知识技能点</t>
+          <t>知识点项目出现记录</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>事务控制语句</t>
+          <t>P08 事务概念与ACID</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -22461,17 +22601,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>KO061</t>
+          <t>CK059</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>知识点项目出现记录</t>
+          <t>规范化知识技能点</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>P08 事务控制语句</t>
+          <t>事务控制语句</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -22488,17 +22628,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CL001</t>
+          <t>KO061</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>非项目技术实训层内容</t>
+          <t>知识点项目出现记录</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>DDL、DML、DCL语言范围</t>
+          <t>P08 事务控制语句</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -22515,7 +22655,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CL002</t>
+          <t>CL001</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -22525,7 +22665,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>权限管理基础目标</t>
+          <t>DDL、DML、DCL语言范围</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -22542,7 +22682,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CL003</t>
+          <t>CL002</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -22552,7 +22692,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>用户权限加密与审计提及</t>
+          <t>权限管理基础目标</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -22569,17 +22709,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CA001</t>
+          <t>CL003</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>教学活动</t>
+          <t>非项目技术实训层内容</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>概念案例讲授与可视化讲解</t>
+          <t>用户权限加密与审计提及</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -22596,7 +22736,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>CA002</t>
+          <t>CA001</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -22606,7 +22746,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>安装配置连接演示</t>
+          <t>概念案例讲授与可视化讲解</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -22623,7 +22763,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CA003</t>
+          <t>CA002</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -22633,7 +22773,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>安装配置连接同步操作</t>
+          <t>安装配置连接演示</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -22650,7 +22790,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CA004</t>
+          <t>CA003</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -22660,7 +22800,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>独立安装并连接服务器</t>
+          <t>安装配置连接同步操作</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -22677,7 +22817,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CA005</t>
+          <t>CA004</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -22687,7 +22827,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>概念模型案例讲解</t>
+          <t>独立安装并连接服务器</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -22704,7 +22844,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CA006</t>
+          <t>CA005</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -22714,7 +22854,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>E-R图工具展示及转换指导</t>
+          <t>概念模型案例讲解</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -22731,7 +22871,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CA007</t>
+          <t>CA006</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -22741,7 +22881,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>案例分析与实操练习</t>
+          <t>E-R图工具展示及转换指导</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -22758,7 +22898,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CA008</t>
+          <t>CA007</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -22768,7 +22908,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>E-R图模式转换与规范化作业</t>
+          <t>案例分析与实操练习</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22785,7 +22925,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CA009</t>
+          <t>CA008</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -22795,7 +22935,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>库表与完整性约束演示</t>
+          <t>E-R图模式转换与规范化作业</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22812,7 +22952,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CA010</t>
+          <t>CA009</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -22822,7 +22962,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>库表创建修改管理</t>
+          <t>库表与完整性约束演示</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22839,7 +22979,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CA011</t>
+          <t>CA010</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -22849,7 +22989,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>完整性约束设置</t>
+          <t>库表创建修改管理</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22866,7 +23006,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CA012</t>
+          <t>CA011</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -22876,7 +23016,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>业务场景库表搭建</t>
+          <t>完整性约束设置</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22893,7 +23033,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CA013</t>
+          <t>CA012</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -22903,7 +23043,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>数据插入修改删除演示</t>
+          <t>业务场景库表搭建</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22920,7 +23060,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CA014</t>
+          <t>CA013</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -22930,7 +23070,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>跟随演示数据操作</t>
+          <t>数据插入修改删除演示</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22947,7 +23087,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CA015</t>
+          <t>CA014</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -22957,7 +23097,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>插入条件更新与删除</t>
+          <t>跟随演示数据操作</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22974,7 +23114,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CA016</t>
+          <t>CA015</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -22984,7 +23124,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>业务数据操作实训</t>
+          <t>插入条件更新与删除</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23001,7 +23141,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CA017</t>
+          <t>CA016</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -23011,7 +23151,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>查询与多表方法讲解</t>
+          <t>业务数据操作实训</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23028,7 +23168,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CA018</t>
+          <t>CA017</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -23038,7 +23178,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>业务查询实验</t>
+          <t>查询与多表方法讲解</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23055,7 +23195,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CA019</t>
+          <t>CA018</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -23065,7 +23205,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>业务场景复杂查询</t>
+          <t>业务查询实验</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23082,7 +23222,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CA020</t>
+          <t>CA019</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -23092,7 +23232,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>视图全流程演示</t>
+          <t>业务场景复杂查询</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23109,7 +23249,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CA021</t>
+          <t>CA020</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -23119,7 +23259,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>创建查询及操作视图</t>
+          <t>视图全流程演示</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23136,7 +23276,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CA022</t>
+          <t>CA021</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -23146,7 +23286,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>多种索引创建演示</t>
+          <t>创建查询及操作视图</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23163,7 +23303,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CA023</t>
+          <t>CA022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -23173,7 +23313,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>索引创建与删除</t>
+          <t>多种索引创建演示</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23190,7 +23330,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CA024</t>
+          <t>CA023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -23200,7 +23340,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>有无索引查询效果对比</t>
+          <t>索引创建与删除</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -23217,7 +23357,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CA025</t>
+          <t>CA024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -23227,7 +23367,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>备份恢复及事务讲解演示</t>
+          <t>有无索引查询效果对比</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -23244,7 +23384,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>CA026</t>
+          <t>CA025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -23254,7 +23394,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>备份恢复和事务操作</t>
+          <t>备份恢复及事务讲解演示</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -23271,17 +23411,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CO001</t>
+          <t>CA026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>学习成果/潜在产物</t>
+          <t>教学活动</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>独立部署并连接的数据库环境</t>
+          <t>备份恢复和事务操作</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -23298,7 +23438,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CO002</t>
+          <t>CO001</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -23308,7 +23448,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>E-R图、关系模式及规范化优化作业</t>
+          <t>独立部署并连接的数据库环境</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -23325,7 +23465,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CO003</t>
+          <t>CO002</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -23335,7 +23475,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>绘图工具输出的设计成果</t>
+          <t>E-R图、关系模式及规范化优化作业</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -23352,7 +23492,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CO004</t>
+          <t>CO003</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -23362,7 +23502,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>已创建修改的库表及约束</t>
+          <t>绘图工具输出的设计成果</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23379,7 +23519,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>CO005</t>
+          <t>CO004</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -23389,7 +23529,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>库表操作SQL记录及结构对照</t>
+          <t>已创建修改的库表及约束</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23406,7 +23546,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CO006</t>
+          <t>CO005</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -23416,7 +23556,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>已完成插入更新删除的数据</t>
+          <t>库表操作SQL记录及结构对照</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23433,7 +23573,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>CO007</t>
+          <t>CO006</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -23443,7 +23583,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>数据操作SQL脚本与前后对照</t>
+          <t>已完成插入更新删除的数据</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23460,7 +23600,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CO008</t>
+          <t>CO007</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -23470,7 +23610,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>业务查询语句</t>
+          <t>数据操作SQL脚本与前后对照</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23487,7 +23627,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CO009</t>
+          <t>CO008</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -23497,7 +23637,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>查询执行结果记录</t>
+          <t>业务查询语句</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23514,7 +23654,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CO010</t>
+          <t>CO009</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -23524,7 +23664,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>已创建查询及操作的视图</t>
+          <t>查询执行结果记录</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23541,7 +23681,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CO011</t>
+          <t>CO010</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -23551,7 +23691,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>索引创建删除操作结果</t>
+          <t>已创建查询及操作的视图</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23568,7 +23708,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CO012</t>
+          <t>CO011</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -23578,7 +23718,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>有无索引效果对比记录</t>
+          <t>索引创建删除操作结果</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23595,7 +23735,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CO013</t>
+          <t>CO012</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -23605,7 +23745,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>备份恢复与事务操作完成结果</t>
+          <t>有无索引效果对比记录</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -23622,7 +23762,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CO014</t>
+          <t>CO013</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -23632,7 +23772,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>数据库备份文件及恢复核对记录</t>
+          <t>备份恢复与事务操作完成结果</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -23649,17 +23789,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>EC001</t>
+          <t>CO014</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>评价/检查/完成要求证据</t>
+          <t>学习成果/潜在产物</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>课堂检查与反馈</t>
+          <t>数据库备份文件及恢复核对记录</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -23676,7 +23816,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>EC002</t>
+          <t>EC001</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -23686,7 +23826,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>课后任务完成要求</t>
+          <t>课堂检查与反馈</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -23703,7 +23843,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>EC003</t>
+          <t>EC002</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -23713,7 +23853,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>独立作业要求</t>
+          <t>课后任务完成要求</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -23730,7 +23870,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>EC004</t>
+          <t>EC003</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -23740,7 +23880,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>教师答疑反馈</t>
+          <t>独立作业要求</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -23757,7 +23897,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>EC005</t>
+          <t>EC004</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -23767,7 +23907,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>课后任务要求</t>
+          <t>教师答疑反馈</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -23784,7 +23924,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>EC006</t>
+          <t>EC005</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -23794,7 +23934,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>操作跟进与答疑</t>
+          <t>课后任务要求</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -23811,7 +23951,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>EC007</t>
+          <t>EC006</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -23821,7 +23961,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>巡查纠错反馈</t>
+          <t>操作跟进与答疑</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -23838,7 +23978,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>EC008</t>
+          <t>EC007</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -23848,7 +23988,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>课后实训要求</t>
+          <t>巡查纠错反馈</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -23865,7 +24005,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>EC009</t>
+          <t>EC008</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -23875,7 +24015,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>实验任务完成要求</t>
+          <t>课后实训要求</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -23892,7 +24032,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>EC010</t>
+          <t>EC009</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -23902,7 +24042,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>随堂巡查答疑</t>
+          <t>实验任务完成要求</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -23919,7 +24059,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>EC011</t>
+          <t>EC010</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -23929,7 +24069,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>专项实验完成要求</t>
+          <t>随堂巡查答疑</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -23946,7 +24086,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>EC012</t>
+          <t>EC011</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -23956,7 +24096,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>操作纠错反馈</t>
+          <t>专项实验完成要求</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -23973,7 +24113,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>EC013</t>
+          <t>EC012</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -23983,7 +24123,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>独立实验完成要求</t>
+          <t>操作纠错反馈</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -24000,7 +24140,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>EC014</t>
+          <t>EC013</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -24010,7 +24150,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>纠错反馈</t>
+          <t>独立实验完成要求</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -24027,7 +24167,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>EC015</t>
+          <t>EC014</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -24037,7 +24177,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>独立实验完成要求</t>
+          <t>纠错反馈</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -24054,7 +24194,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>EC016</t>
+          <t>EC015</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -24064,7 +24204,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>答疑纠错反馈</t>
+          <t>独立实验完成要求</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -24081,7 +24221,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>EC017</t>
+          <t>EC016</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -24091,7 +24231,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>考核章节仅文本层标题</t>
+          <t>答疑纠错反馈</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -24108,17 +24248,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>PT01</t>
+          <t>EC017</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>独立实训文本层候选</t>
+          <t>评价/检查/完成要求证据</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>实训一：数据定义</t>
+          <t>考核章节仅文本层标题</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -24135,17 +24275,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>PT01-OP1</t>
+          <t>PT01</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>实训操作文本层候选</t>
+          <t>独立实训文本层候选</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>使用SQL语言，创建数据库；</t>
+          <t>实训一：数据定义</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -24162,7 +24302,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>PT01-OP2</t>
+          <t>PT01-OP1</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -24172,7 +24312,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>使用CREATETABLE语句，创建多张表；</t>
+          <t>使用SQL语言，创建数据库；</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -24189,7 +24329,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>PT01-OP3</t>
+          <t>PT01-OP2</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -24199,7 +24339,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>使用ALTERTABLE语句，修改表结构；</t>
+          <t>使用CREATETABLE语句，创建多张表；</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -24216,17 +24356,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PT02</t>
+          <t>PT01-OP3</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>独立实训文本层候选</t>
+          <t>实训操作文本层候选</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>实训二：数据操作</t>
+          <t>使用ALTERTABLE语句，修改表结构；</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -24243,17 +24383,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>PT02-OP1</t>
+          <t>PT02</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>实训操作文本层候选</t>
+          <t>独立实训文本层候选</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>使用INERTINTO语句，插入样本数据；</t>
+          <t>实训二：数据操作</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -24270,7 +24410,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>PT02-OP2</t>
+          <t>PT02-OP1</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -24280,7 +24420,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>使用UPDATE语句，修改数据；</t>
+          <t>使用INERTINTO语句，插入样本数据；</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -24297,7 +24437,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>PT02-OP3</t>
+          <t>PT02-OP2</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -24307,7 +24447,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>使用DELETEFROM语句，删除数据；</t>
+          <t>使用UPDATE语句，修改数据；</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -24324,17 +24464,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>PT03</t>
+          <t>PT02-OP3</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>独立实训文本层候选</t>
+          <t>实训操作文本层候选</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>实训三：数据查询</t>
+          <t>使用DELETEFROM语句，删除数据；</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -24351,32 +24491,113 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
+          <t>PT03</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>独立实训文本层候选</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>实训三：数据查询</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>DOC01</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>待研究者审查；非已确认教学效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
           <t>PT03-OP1</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>实训操作文本层候选</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C228" t="inlineStr">
         <is>
           <t>使用SELECT语句对数据库完成相应查询，包括：列查询、条件查询、多表连接和分类查询与汇总。</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>DOC01</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DOC01</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
         <is>
           <t>待研究者审查；非已确认教学效果</t>
         </is>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CTB001</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>知识技能点技术行为接口</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>备份相关技术行为</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>DOC01</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>待研究者审查；非已确认教学效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>CTB002</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>知识技能点技术行为接口</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>恢复相关技术行为</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>DOC01</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>待研究者审查；非已确认教学效果</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E227"/>
+  <autoFilter ref="A1:E230"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24387,7 +24608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E243"/>
+  <dimension ref="A1:E245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -28374,7 +28595,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CK015</t>
+          <t>CK060</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -30958,8 +31179,62 @@
         </is>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>CK057</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>CTB001</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>包含技术行为接口</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>研究组织标签，非能力支持等级</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>待研究者审查</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>CK057</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>CTB002</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>包含技术行为接口</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>研究组织标签，非能力支持等级</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>待研究者审查</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E243"/>
+  <autoFilter ref="A1:E245"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30970,7 +31245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -30992,113 +31267,137 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CKxxx</t>
+          <t>应用语境标签</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>规范化知识点实体；固定ID来自人工清单，不因多项目出现而复制</t>
+          <t>同一知识在不同项目的用途，非新岗位能力</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KOxxx</t>
+          <t>CTBxxx</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>知识点在具体项目的出现记录，独立于CK</t>
+          <t>CK057备份/恢复技术行为接口；原文明示独立实验，标签为研究组织，不判支持等级</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAxxx/COxxx/CExx-hash</t>
+          <t>CKxxx</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>活动/成果/证据；证据号为页码＋摘录哈希，页码相同但原文不同可区分</t>
+          <t>规范化知识点实体；固定ID来自人工清单，不因多项目出现而复制</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>来源证据层</t>
+          <t>KOxxx</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>可见PDF原文与隐藏文本候选分开；课程目标不等于项目实践</t>
+          <t>知识点在具体项目的出现记录，独立于CK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>成果证据性质</t>
+          <t>CAxxx/COxxx/CExx-hash</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>明确产物/可直接确认技术结果/研究推断潜在产物分开，均非学生实际表现</t>
+          <t>活动/成果/证据；证据号为页码＋摘录哈希，页码相同但原文不同可区分</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>课程功能标签</t>
+          <t>来源证据层</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>课程内容组织标签，非岗位A/B/C等级或重要性排名</t>
+          <t>可见PDF原文与隐藏文本候选分开；课程目标不等于项目实践</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PRACTICE32同源组</t>
+          <t>成果证据性质</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>学时同源、不重复累计：8项目实践32与3实训32为同一批实践学时；课程64=理论32+实践32，禁止相加为96。</t>
+          <t>明确产物/可直接确认技术结果/研究推断潜在产物分开，均非学生实际表现</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>关联状态</t>
+          <t>课程功能标签</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>内容相关不等于精确学时对应；研究组织关联不等于原文明示评分绑定</t>
+          <t>课程内容组织标签，非岗位A/B/C等级或重要性排名</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>PRACTICE32同源组</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>学时同源、不重复累计：8项目实践32与3实训32为同一批实践学时；课程64=理论32+实践32，禁止相加为96。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>关联状态</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>内容相关不等于精确学时对应；研究组织关联不等于原文明示评分绑定</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>评分规则</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>没有可读原文则标未提供或无法确认，不凭教学常识补写</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10"/>
+  <autoFilter ref="A1:B12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>